--- a/output/pdf_financials_xlsx/TOC.xlsx
+++ b/output/pdf_financials_xlsx/TOC.xlsx
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.360247</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.074886</v>
       </c>
     </row>
     <row r="93">
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.65</v>
+        <v>-0.301437</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.33</v>
+        <v>-1.217006</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.26</v>
+        <v>-1.131717</v>
       </c>
     </row>
     <row r="119">
@@ -3310,7 +3310,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4065,7 +4069,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -4803,7 +4811,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
         <v>-0.951437</v>
       </c>

--- a/output/pdf_financials_xlsx/TOC.xlsx
+++ b/output/pdf_financials_xlsx/TOC.xlsx
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.101639</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.903693</v>
       </c>
     </row>
     <row r="35">
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.101639</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.903693</v>
       </c>
     </row>
     <row r="37">
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.822464</v>
+        <v>0.720825</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.424011</v>
+        <v>2.520318</v>
       </c>
     </row>
     <row r="49">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">

--- a/output/pdf_financials_xlsx/TOC.xlsx
+++ b/output/pdf_financials_xlsx/TOC.xlsx
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.744429</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.468767</v>
       </c>
     </row>
     <row r="65">
@@ -1575,16 +1575,14 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.079137</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.13484</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.14873</v>
       </c>
     </row>
     <row r="68">
